--- a/data/trans_bre/PCS12_SP_R3-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/PCS12_SP_R3-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,58; 14,31</t>
+          <t>5,5; 14,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,47; 17,26</t>
+          <t>7,61; 16,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,94; 15,46</t>
+          <t>6,03; 15,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,92; 9,46</t>
+          <t>0,75; 10,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>29,22; 95,25</t>
+          <t>29,14; 92,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,45; 104,81</t>
+          <t>36,4; 99,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,98; 92,23</t>
+          <t>27,24; 90,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,98; 38,83</t>
+          <t>2,42; 43,6</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,88; 17,01</t>
+          <t>9,52; 17,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,43; 14,58</t>
+          <t>6,85; 14,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,17; 13,74</t>
+          <t>6,57; 13,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-36,48; 12,63</t>
+          <t>-37,48; 12,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>62,27; 133,62</t>
+          <t>59,06; 138,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,89; 88,87</t>
+          <t>33,09; 88,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,47; 92,63</t>
+          <t>37,33; 95,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-55,44; 71,61</t>
+          <t>-57,18; 71,03</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,99; 15,98</t>
+          <t>7,09; 16,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,89; 16,45</t>
+          <t>7,93; 16,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,44; 12,71</t>
+          <t>4,46; 12,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,51; 7,31</t>
+          <t>-11,31; 6,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>36,31; 107,87</t>
+          <t>36,47; 109,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>48,35; 136,1</t>
+          <t>46,73; 132,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,08; 99,29</t>
+          <t>23,38; 96,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-47,03; 37,1</t>
+          <t>-47,1; 34,09</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,46; 14,22</t>
+          <t>7,37; 14,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,66; 14,06</t>
+          <t>6,08; 13,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,63; 12,26</t>
+          <t>4,65; 12,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,27; 12,75</t>
+          <t>3,09; 13,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>44,6; 104,89</t>
+          <t>42,54; 103,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,71; 82,14</t>
+          <t>28,0; 79,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,92; 83,46</t>
+          <t>24,74; 85,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,31; 64,0</t>
+          <t>14,36; 66,79</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,49; 13,38</t>
+          <t>9,34; 13,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,16; 13,2</t>
+          <t>9,2; 13,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,46; 11,44</t>
+          <t>7,57; 11,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-14,7; 7,8</t>
+          <t>-16,83; 7,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>57,57; 91,53</t>
+          <t>55,46; 90,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,15; 79,32</t>
+          <t>48,41; 79,76</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,2; 72,34</t>
+          <t>43,22; 73,27</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-34,03; 35,88</t>
+          <t>-39,44; 36,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/PCS12_SP_R3-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/PCS12_SP_R3-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,38</t>
+          <t>4,97</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>18,59%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,5; 14,56</t>
+          <t>5,86; 14,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,61; 16,64</t>
+          <t>7,16; 16,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,03; 15,45</t>
+          <t>5,64; 15,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,75; 10,39</t>
+          <t>0,67; 9,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>29,14; 92,3</t>
+          <t>29,3; 92,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,4; 99,42</t>
+          <t>32,67; 101,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,24; 90,16</t>
+          <t>26,9; 90,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,42; 43,6</t>
+          <t>2,31; 38,86</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-5,12</t>
+          <t>11,69</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-14,57%</t>
+          <t>64,11%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,52; 17,27</t>
+          <t>9,29; 16,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,85; 14,85</t>
+          <t>6,9; 14,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,57; 13,69</t>
+          <t>6,22; 13,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-37,48; 12,71</t>
+          <t>8,32; 15,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>59,06; 138,02</t>
+          <t>58,02; 136,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,09; 88,2</t>
+          <t>33,29; 88,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,33; 95,61</t>
+          <t>34,79; 90,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-57,18; 71,03</t>
+          <t>40,88; 94,16</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,56</t>
+          <t>6,34</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-2,67%</t>
+          <t>31,24%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,09; 16,17</t>
+          <t>6,55; 15,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,93; 16,46</t>
+          <t>7,77; 16,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,46; 12,7</t>
+          <t>4,86; 12,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,31; 6,76</t>
+          <t>2,37; 10,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>36,47; 109,33</t>
+          <t>33,25; 104,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>46,73; 132,44</t>
+          <t>46,62; 133,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,38; 96,48</t>
+          <t>29,59; 100,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-47,1; 34,09</t>
+          <t>10,4; 57,91</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9,09</t>
+          <t>11,43</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>54,2%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,37; 14,55</t>
+          <t>7,3; 14,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,08; 13,85</t>
+          <t>6,35; 14,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,65; 12,49</t>
+          <t>5,01; 12,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,09; 13,29</t>
+          <t>7,85; 14,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>42,54; 103,58</t>
+          <t>42,69; 106,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,0; 79,25</t>
+          <t>29,7; 84,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,74; 85,33</t>
+          <t>27,25; 82,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,36; 66,79</t>
+          <t>33,93; 76,39</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,06</t>
+          <t>9,17</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>43,35%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,34; 13,56</t>
+          <t>9,48; 13,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,2; 13,57</t>
+          <t>9,09; 13,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,57; 11,55</t>
+          <t>7,3; 11,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-16,83; 7,78</t>
+          <t>7,25; 11,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>55,46; 90,75</t>
+          <t>56,68; 90,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,41; 79,76</t>
+          <t>48,37; 78,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,22; 73,27</t>
+          <t>41,43; 72,66</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-39,44; 36,29</t>
+          <t>32,8; 55,14</t>
         </is>
       </c>
     </row>
